--- a/Parser2/Example/Instruction/Instruction.xlsx
+++ b/Parser2/Example/Instruction/Instruction.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\Instruction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A511422D-9317-4327-8F32-B1EE26710959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2320D0-CF81-4C9D-B101-7C827757D793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="945" windowWidth="16800" windowHeight="9480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lvl0" sheetId="1" r:id="rId1"/>
-    <sheet name="Lvl1" sheetId="2" r:id="rId2"/>
-    <sheet name="Lvl2" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="5" r:id="rId4"/>
+    <sheet name="Lvl1" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
   <si>
     <t>ignore</t>
   </si>
@@ -45,46 +43,52 @@
     <t>value</t>
   </si>
   <si>
-    <t>aliasFuncArg</t>
-  </si>
-  <si>
-    <t>arg1</t>
-  </si>
-  <si>
-    <t>arg2</t>
-  </si>
-  <si>
-    <t>arg3</t>
-  </si>
-  <si>
-    <t>field1</t>
-  </si>
-  <si>
-    <t>field2</t>
-  </si>
-  <si>
-    <t>field3</t>
-  </si>
-  <si>
-    <t>field4</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
     <t>str</t>
   </si>
   <si>
     <t>num</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
     <t>example1</t>
+  </si>
+  <si>
+    <t>Igor</t>
+  </si>
+  <si>
+    <t>surname</t>
+  </si>
+  <si>
+    <t>Skladchikov</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>example1_adress</t>
+  </si>
+  <si>
+    <t>Example1. Parsing target json</t>
+  </si>
+  <si>
+    <t>This row start parsing</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Russian</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Saint Petersburg</t>
   </si>
 </sst>
 </file>
@@ -100,55 +104,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -157,13 +148,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,117 +438,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <mergeCells count="2">
+    <mergeCell ref="B7:XFD7"/>
+    <mergeCell ref="B5:XFD5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B03B707-67CF-4B7A-9143-21C9D82C9ABB}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F53452A-0517-441C-A9CB-5EB42226E399}">
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C4B254-87AC-43D9-8221-E934A2486486}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCBED238-0F70-461A-B69F-AA217AA5E879}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B5:XFD5"/>
+    <mergeCell ref="B7:XFD7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Parser2/Example/Instruction/Instruction.xlsx
+++ b/Parser2/Example/Instruction/Instruction.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\Instruction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2320D0-CF81-4C9D-B101-7C827757D793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE4770A-A58E-4879-9D98-EE574D6B5163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="945" windowWidth="16800" windowHeight="9480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4545" yWindow="945" windowWidth="16800" windowHeight="9480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lvl0" sheetId="1" r:id="rId1"/>
     <sheet name="Lvl1" sheetId="7" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>ignore</t>
   </si>
@@ -89,6 +89,48 @@
   </si>
   <si>
     <t>Saint Petersburg</t>
+  </si>
+  <si>
+    <t>Example2. Types</t>
+  </si>
+  <si>
+    <t>example2</t>
+  </si>
+  <si>
+    <t>stringField</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>numberField</t>
+  </si>
+  <si>
+    <t>booleanField</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>nullField</t>
+  </si>
+  <si>
+    <t>objectField</t>
+  </si>
+  <si>
+    <t>arrayField</t>
+  </si>
+  <si>
+    <t>arr</t>
+  </si>
+  <si>
+    <t>example2_arrField</t>
+  </si>
+  <si>
+    <t>example2_objField</t>
+  </si>
+  <si>
+    <t>$null</t>
   </si>
 </sst>
 </file>
@@ -151,11 +193,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -438,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
@@ -465,19 +507,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -528,10 +570,91 @@
         <v>14</v>
       </c>
     </row>
+    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B7:XFD7"/>
     <mergeCell ref="B5:XFD5"/>
+    <mergeCell ref="B13:XFD13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -567,20 +690,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
+      <c r="B5" s="4" t="str">
+        <f>Lvl0!B5</f>
+        <v>This row start parsing</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>Lvl0!B7</f>
+        <v>Example1. Parsing target json</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">

--- a/Parser2/Example/Instruction/Instruction.xlsx
+++ b/Parser2/Example/Instruction/Instruction.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyFolder\Projects\ExcelToJsonUniversalParser\Repo\Parser2\Example\Instruction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE4770A-A58E-4879-9D98-EE574D6B5163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF95A740-9044-4138-B099-13473451B2D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4545" yWindow="945" windowWidth="16800" windowHeight="9480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="735" windowWidth="16800" windowHeight="9120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lvl0" sheetId="1" r:id="rId1"/>
     <sheet name="Lvl1" sheetId="7" r:id="rId2"/>
+    <sheet name="Lvl2" sheetId="8" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="48">
   <si>
     <t>ignore</t>
   </si>
@@ -91,9 +92,6 @@
     <t>Saint Petersburg</t>
   </si>
   <si>
-    <t>Example2. Types</t>
-  </si>
-  <si>
     <t>example2</t>
   </si>
   <si>
@@ -130,7 +128,49 @@
     <t>example2_objField</t>
   </si>
   <si>
-    <t>$null</t>
+    <t>null</t>
+  </si>
+  <si>
+    <t>subfield1</t>
+  </si>
+  <si>
+    <t>subfield2</t>
+  </si>
+  <si>
+    <t>text1</t>
+  </si>
+  <si>
+    <t>item1</t>
+  </si>
+  <si>
+    <t>item2</t>
+  </si>
+  <si>
+    <t>item3</t>
+  </si>
+  <si>
+    <t>item4</t>
+  </si>
+  <si>
+    <t>item5</t>
+  </si>
+  <si>
+    <t>objArrayField</t>
+  </si>
+  <si>
+    <t>example2_objArrayField</t>
+  </si>
+  <si>
+    <t>example2_objArrayField_item1</t>
+  </si>
+  <si>
+    <t>example2_objArrayField_item2</t>
+  </si>
+  <si>
+    <t>example2_objArrayField_item3</t>
+  </si>
+  <si>
+    <t>Example2. Types variation</t>
   </si>
 </sst>
 </file>
@@ -190,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -198,6 +238,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -480,12 +524,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
@@ -515,7 +562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" s="3" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="b">
         <v>1</v>
       </c>
@@ -523,7 +570,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>7</v>
       </c>
@@ -537,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -548,7 +595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>11</v>
       </c>
@@ -559,7 +606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>12</v>
       </c>
@@ -570,91 +617,98 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="12" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
         <v>23</v>
       </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" t="s">
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" t="s">
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
         <v>28</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
       </c>
       <c r="D19" t="s">
         <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" t="s">
         <v>30</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>31</v>
       </c>
-      <c r="E20" t="s">
-        <v>32</v>
-      </c>
-    </row>
+    </row>
+    <row r="21" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B7:XFD7"/>
     <mergeCell ref="B5:XFD5"/>
-    <mergeCell ref="B13:XFD13"/>
+    <mergeCell ref="B14:XFD14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -663,13 +717,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F53452A-0517-441C-A9CB-5EB42226E399}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -699,7 +756,7 @@
         <v>This row start parsing</v>
       </c>
     </row>
-    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" s="3" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="b">
         <v>1</v>
       </c>
@@ -708,7 +765,7 @@
         <v>Example1. Parsing target json</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -722,7 +779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>19</v>
       </c>
@@ -733,6 +790,243 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <f>Lvl0!B14</f>
+        <v>Example2. Types variation</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B5:XFD5"/>
+    <mergeCell ref="B7:XFD7"/>
+    <mergeCell ref="B12:XFD12"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90B4032F-FD98-457B-B53A-409A5704420A}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <f>'Lvl1'!B5:XFD5</f>
+        <v>This row start parsing</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>'Lvl1'!B12:XFD12</f>
+        <v>Example2. Types variation</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B5:XFD5"/>
